--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P540"/>
+  <dimension ref="A1:P547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29590,6 +29590,384 @@
         <v>334.16</v>
       </c>
       <c r="P540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="C541" t="n">
+        <v>333.18</v>
+      </c>
+      <c r="D541" t="n">
+        <v>339.72</v>
+      </c>
+      <c r="E541" t="n">
+        <v>348.23</v>
+      </c>
+      <c r="F541" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="G541" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="H541" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="I541" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="J541" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="K541" t="n">
+        <v>347.35</v>
+      </c>
+      <c r="L541" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="M541" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="N541" t="n">
+        <v>327.05</v>
+      </c>
+      <c r="O541" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="C542" t="n">
+        <v>333.27</v>
+      </c>
+      <c r="D542" t="n">
+        <v>339.69</v>
+      </c>
+      <c r="E542" t="n">
+        <v>348.15</v>
+      </c>
+      <c r="F542" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G542" t="n">
+        <v>336.98</v>
+      </c>
+      <c r="H542" t="n">
+        <v>343.52</v>
+      </c>
+      <c r="I542" t="n">
+        <v>341.63</v>
+      </c>
+      <c r="J542" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="K542" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="L542" t="n">
+        <v>349.94</v>
+      </c>
+      <c r="M542" t="n">
+        <v>338.95</v>
+      </c>
+      <c r="N542" t="n">
+        <v>326.87</v>
+      </c>
+      <c r="O542" t="n">
+        <v>331.78</v>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="C543" t="n">
+        <v>332.69</v>
+      </c>
+      <c r="D543" t="n">
+        <v>338.78</v>
+      </c>
+      <c r="E543" t="n">
+        <v>348.63</v>
+      </c>
+      <c r="F543" t="n">
+        <v>336.51</v>
+      </c>
+      <c r="G543" t="n">
+        <v>336.34</v>
+      </c>
+      <c r="H543" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="I543" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="J543" t="n">
+        <v>341.84</v>
+      </c>
+      <c r="K543" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="L543" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="M543" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="N543" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="O543" t="n">
+        <v>331.56</v>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>344.86</v>
+      </c>
+      <c r="C544" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="D544" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="E544" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="F544" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="G544" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="H544" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="I544" t="n">
+        <v>341.2</v>
+      </c>
+      <c r="J544" t="n">
+        <v>342.32</v>
+      </c>
+      <c r="K544" t="n">
+        <v>344.63</v>
+      </c>
+      <c r="L544" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="M544" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="N544" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="O544" t="n">
+        <v>332.04</v>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="C545" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="D545" t="n">
+        <v>339.85</v>
+      </c>
+      <c r="E545" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="F545" t="n">
+        <v>337.7</v>
+      </c>
+      <c r="G545" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="H545" t="n">
+        <v>343.36</v>
+      </c>
+      <c r="I545" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="J545" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="K545" t="n">
+        <v>344.74</v>
+      </c>
+      <c r="L545" t="n">
+        <v>349.72</v>
+      </c>
+      <c r="M545" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="N545" t="n">
+        <v>324.49</v>
+      </c>
+      <c r="O545" t="n">
+        <v>332.33</v>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>345.66</v>
+      </c>
+      <c r="C546" t="n">
+        <v>333.54</v>
+      </c>
+      <c r="D546" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="E546" t="n">
+        <v>350.71</v>
+      </c>
+      <c r="F546" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="G546" t="n">
+        <v>337.72</v>
+      </c>
+      <c r="H546" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="I546" t="n">
+        <v>341.62</v>
+      </c>
+      <c r="J546" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="K546" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="L546" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="M546" t="n">
+        <v>338</v>
+      </c>
+      <c r="N546" t="n">
+        <v>324.85</v>
+      </c>
+      <c r="O546" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="C547" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="D547" t="n">
+        <v>339.8</v>
+      </c>
+      <c r="E547" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="F547" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="G547" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="H547" t="n">
+        <v>343.56</v>
+      </c>
+      <c r="I547" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="J547" t="n">
+        <v>342.3</v>
+      </c>
+      <c r="K547" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="L547" t="n">
+        <v>350.16</v>
+      </c>
+      <c r="M547" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="N547" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="O547" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="P547" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29606,7 +29984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35079,6 +35457,76 @@
       </c>
       <c r="B547" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -35247,28 +35695,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03886741361379183</v>
+        <v>-0.04292552821238704</v>
       </c>
       <c r="J2" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003567902085048424</v>
+        <v>0.004455330438971727</v>
       </c>
       <c r="M2" t="n">
-        <v>4.134677755978825</v>
+        <v>4.102105928684986</v>
       </c>
       <c r="N2" t="n">
-        <v>25.65597802425262</v>
+        <v>25.39716114449232</v>
       </c>
       <c r="O2" t="n">
-        <v>5.065173049783454</v>
+        <v>5.039559618110725</v>
       </c>
       <c r="P2" t="n">
-        <v>346.683493774493</v>
+        <v>346.7246506682147</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35325,28 +35773,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04611812397290446</v>
+        <v>-0.0615020504589136</v>
       </c>
       <c r="J3" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K3" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005603971237536864</v>
+        <v>0.009961852078737343</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8004530738589</v>
+        <v>3.817662603952982</v>
       </c>
       <c r="N3" t="n">
-        <v>22.95034708613656</v>
+        <v>23.18804198262488</v>
       </c>
       <c r="O3" t="n">
-        <v>4.790652052292732</v>
+        <v>4.815396347407436</v>
       </c>
       <c r="P3" t="n">
-        <v>340.7728202008457</v>
+        <v>340.9290037330206</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35403,28 +35851,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02718046278127911</v>
+        <v>0.007875499254918535</v>
       </c>
       <c r="J4" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001824000162243045</v>
+        <v>0.000152339729354134</v>
       </c>
       <c r="M4" t="n">
-        <v>4.003895416780034</v>
+        <v>4.061389843119703</v>
       </c>
       <c r="N4" t="n">
-        <v>24.58546654043382</v>
+        <v>25.11018379761049</v>
       </c>
       <c r="O4" t="n">
-        <v>4.958373376464687</v>
+        <v>5.011006265971984</v>
       </c>
       <c r="P4" t="n">
-        <v>347.1332176137396</v>
+        <v>347.3291994688119</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35481,28 +35929,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1288351764568476</v>
+        <v>0.1121951944996829</v>
       </c>
       <c r="J5" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K5" t="n">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0379683985197482</v>
+        <v>0.02912776496195235</v>
       </c>
       <c r="M5" t="n">
-        <v>4.119818518340225</v>
+        <v>4.164035823208909</v>
       </c>
       <c r="N5" t="n">
-        <v>25.61927987591532</v>
+        <v>25.9243531453828</v>
       </c>
       <c r="O5" t="n">
-        <v>5.061549157710051</v>
+        <v>5.091596325847405</v>
       </c>
       <c r="P5" t="n">
-        <v>352.9593077080427</v>
+        <v>353.1280944810386</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35559,28 +36007,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1719671466884463</v>
+        <v>0.1498021174964978</v>
       </c>
       <c r="J6" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K6" t="n">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0545520470488623</v>
+        <v>0.04161867933090724</v>
       </c>
       <c r="M6" t="n">
-        <v>4.481794057705518</v>
+        <v>4.549860667936565</v>
       </c>
       <c r="N6" t="n">
-        <v>31.22112087049809</v>
+        <v>31.92937722040504</v>
       </c>
       <c r="O6" t="n">
-        <v>5.587586318840908</v>
+        <v>5.650608570800586</v>
       </c>
       <c r="P6" t="n">
-        <v>342.044085246606</v>
+        <v>342.2689334369772</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35637,28 +36085,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2199087621251933</v>
+        <v>0.1962946622348288</v>
       </c>
       <c r="J7" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K7" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07127863902631815</v>
+        <v>0.05733090743621372</v>
       </c>
       <c r="M7" t="n">
-        <v>5.02142900626366</v>
+        <v>5.096640339397872</v>
       </c>
       <c r="N7" t="n">
-        <v>38.44970168531589</v>
+        <v>39.21261972650618</v>
       </c>
       <c r="O7" t="n">
-        <v>6.20078234461716</v>
+        <v>6.261998061841458</v>
       </c>
       <c r="P7" t="n">
-        <v>341.2999380783686</v>
+        <v>341.5393297272922</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35715,28 +36163,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1944181123152635</v>
+        <v>0.1749975567224284</v>
       </c>
       <c r="J8" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K8" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05598658986856797</v>
+        <v>0.04607623462873567</v>
       </c>
       <c r="M8" t="n">
-        <v>5.119243157969976</v>
+        <v>5.153537934916741</v>
       </c>
       <c r="N8" t="n">
-        <v>38.89103162192021</v>
+        <v>39.24091117435381</v>
       </c>
       <c r="O8" t="n">
-        <v>6.236267443104105</v>
+        <v>6.264256633819675</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5001752287379</v>
+        <v>346.6970592230618</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35793,28 +36241,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2454094133711181</v>
+        <v>0.226694734036149</v>
       </c>
       <c r="J9" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K9" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07705883346146003</v>
+        <v>0.06707388795918534</v>
       </c>
       <c r="M9" t="n">
-        <v>5.503955781795808</v>
+        <v>5.539695963301988</v>
       </c>
       <c r="N9" t="n">
-        <v>44.01653917817787</v>
+        <v>44.23999373489004</v>
       </c>
       <c r="O9" t="n">
-        <v>6.634496151041001</v>
+        <v>6.651315188358618</v>
       </c>
       <c r="P9" t="n">
-        <v>342.7896945541621</v>
+        <v>342.9794257567626</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35871,28 +36319,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3106799806081842</v>
+        <v>0.2916490518507736</v>
       </c>
       <c r="J10" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K10" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1116866213662842</v>
+        <v>0.1006145189011413</v>
       </c>
       <c r="M10" t="n">
-        <v>5.766519725647219</v>
+        <v>5.800010841015016</v>
       </c>
       <c r="N10" t="n">
-        <v>46.84610197698625</v>
+        <v>47.05922606452339</v>
       </c>
       <c r="O10" t="n">
-        <v>6.844421230241915</v>
+        <v>6.85997274517351</v>
       </c>
       <c r="P10" t="n">
-        <v>342.1320271072261</v>
+        <v>342.3249623111168</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35949,28 +36397,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3541550596219488</v>
+        <v>0.3275767938355374</v>
       </c>
       <c r="J11" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K11" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1249021750423126</v>
+        <v>0.1085620249559397</v>
       </c>
       <c r="M11" t="n">
-        <v>6.112859593044048</v>
+        <v>6.183971085176525</v>
       </c>
       <c r="N11" t="n">
-        <v>53.62352700756275</v>
+        <v>54.53532136229497</v>
       </c>
       <c r="O11" t="n">
-        <v>7.322808682982422</v>
+        <v>7.384803407152757</v>
       </c>
       <c r="P11" t="n">
-        <v>347.3059827359069</v>
+        <v>347.5754551558657</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36027,28 +36475,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3971745904237172</v>
+        <v>0.3716207878764427</v>
       </c>
       <c r="J12" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K12" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1435293872121748</v>
+        <v>0.1281135580689307</v>
       </c>
       <c r="M12" t="n">
-        <v>6.244282266869703</v>
+        <v>6.293936727486058</v>
       </c>
       <c r="N12" t="n">
-        <v>57.24229763948645</v>
+        <v>57.97461563866174</v>
       </c>
       <c r="O12" t="n">
-        <v>7.565863971780517</v>
+        <v>7.614106358507329</v>
       </c>
       <c r="P12" t="n">
-        <v>349.9921435397378</v>
+        <v>350.2515708911938</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36105,28 +36553,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3875760508548088</v>
+        <v>0.3620381836806866</v>
       </c>
       <c r="J13" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K13" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0924549364056293</v>
+        <v>0.08244302959850947</v>
       </c>
       <c r="M13" t="n">
-        <v>7.747190538419711</v>
+        <v>7.770105447083965</v>
       </c>
       <c r="N13" t="n">
-        <v>89.66737799524442</v>
+        <v>89.98308902423658</v>
       </c>
       <c r="O13" t="n">
-        <v>9.469286034081156</v>
+        <v>9.485941651951933</v>
       </c>
       <c r="P13" t="n">
-        <v>338.7502662061236</v>
+        <v>339.0095452266918</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36183,28 +36631,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2330981072628262</v>
+        <v>0.2122059601800601</v>
       </c>
       <c r="J14" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K14" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02112238812415612</v>
+        <v>0.01792833150585493</v>
       </c>
       <c r="M14" t="n">
-        <v>10.24817061314303</v>
+        <v>10.2095443549541</v>
       </c>
       <c r="N14" t="n">
-        <v>153.1247458432117</v>
+        <v>152.1568507356248</v>
       </c>
       <c r="O14" t="n">
-        <v>12.37435840127526</v>
+        <v>12.33518750305908</v>
       </c>
       <c r="P14" t="n">
-        <v>327.7897015486436</v>
+        <v>328.0018320828246</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36261,28 +36709,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1858782458338435</v>
+        <v>0.1689992136964681</v>
       </c>
       <c r="J15" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K15" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03955066589641831</v>
+        <v>0.03338585139544747</v>
       </c>
       <c r="M15" t="n">
-        <v>5.925370517973944</v>
+        <v>5.932632069762017</v>
       </c>
       <c r="N15" t="n">
-        <v>51.02233147589978</v>
+        <v>51.00739061234274</v>
       </c>
       <c r="O15" t="n">
-        <v>7.142991773472778</v>
+        <v>7.141945856161522</v>
       </c>
       <c r="P15" t="n">
-        <v>334.2073352229538</v>
+        <v>334.3786908014668</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36320,7 +36768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P540"/>
+  <dimension ref="A1:P547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80555,6 +81003,580 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-34.98991535300299,173.7097688568117</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-34.99066625378229,173.70970294339335</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-34.99141240574582,173.70988736557317</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-34.99214079145849,173.71021832576594</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-34.99281518229462,173.71067426218295</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-34.993401559307785,173.7112217182706</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-34.99395594488184,173.71184398027034</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-34.99447896583445,173.71249922851138</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-34.994977352676244,173.7131552361454</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-34.99546575259817,173.7138316493559</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-34.995939879193074,173.71453478674903</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-34.99642984864124,173.7152308714851</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-34.99692773674623,173.71591642468093</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>-34.997271470739,173.71671895985673</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-34.989915404152775,173.70976710482674</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-34.99066618814682,173.70970392628328</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-34.99141245754183,173.70988704294535</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-34.99214110781524,173.71021753799184</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-34.9928156723933,173.71067347618043</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-34.993403158812754,173.711219204458</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-34.99395772101438,173.71184164812692</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-34.99448081443755,173.7124971388507</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-34.99497871931662,173.71315364340148</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-34.99547070549192,173.71382605365696</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-34.99594282757825,173.71453207636716</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>-34.99643280243078,173.71522855242864</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>-34.99692911539169,173.71591538379738</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>-34.99727332886202,173.71671761176947</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-34.98991498536312,173.70978144920363</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-34.99066661113085,173.7096975921037</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-34.991414028686684,173.70987725656806</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-34.99213920967468,173.7102222646362</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-34.99281561793789,173.71067356351406</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-34.99340668875456,173.7112136567333</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-34.993961824492885,173.711836260071</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-34.99448675637586,173.71249042208353</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-34.99498268908142,173.71314901685935</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-34.99548107354868,173.71381433999173</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-34.99595066596779,173.71452487071684</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-34.996442724133765,173.71522076277617</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-34.99694650164192,173.7159022570965</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-34.99727503214145,173.71671637602276</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-34.98991437795526,173.7098022540248</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-34.990666691351905,173.7096963907938</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-34.99141390782942,173.70987800936632</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-34.99213699517714,173.71022777905435</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-34.99281251397954,173.71067854152986</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-34.99340437223027,173.71121729742768</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-34.993959987114486,173.7118386726334</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-34.99448365336368,173.7124939297287</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-34.99497956533208,173.7131526574171</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-34.99548371509164,173.71381135561793</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-34.99594721419997,173.71452804384742</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-34.9964389372243,173.71522373592617</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-34.99695071416928,173.7158990766175</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-34.99727131589542,173.71671907219732</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-34.98991413818803,173.7098104664541</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-34.9906663558819,173.70970141445346</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-34.99141218129648,173.70988876362702</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-34.99213375251959,173.7102358537375</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-34.99280913774391,173.71068395621327</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-34.99340100775435,173.7112225851025</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-34.99395870094957,173.71184036142705</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-34.99448213486832,173.71249564623585</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-34.99497852408228,173.71315387093634</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-34.99548298866733,173.71381217632077</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-34.99594440963856,173.71453062201584</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-34.99643984608257,173.71522302237022</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>-34.996947344147394,173.71590162100074</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>-34.99726907066339,173.71672070113604</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-34.989914122203515,173.70981101394935</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-34.990665991240355,173.70970687495307</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-34.99141067921208,173.7098981198335</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-34.99213098439686,173.71024274675918</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-34.99280641497309,173.71068832289313</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-34.99339907731723,173.71122561901407</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-34.993955577406126,173.71184446278278</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-34.9944808804591,173.71249706421995</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-34.9949781336136,173.71315432600602</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-34.99548008297006,173.71381545913184</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-34.99594167698893,173.7145331340772</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-34.99643999755896,173.71522290344421</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>-34.99694458685672,173.71590370276868</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>-34.99726938035058,173.71672047645484</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-34.9899144067273,173.70980126853328</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-34.990666756987316,173.70969540790384</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-34.99141226762317,173.709888225914</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-34.99213236845828,173.7102393002484</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-34.99280799418019,173.71068579021883</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-34.99340012526883,173.71122397203354</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-34.993957476030594,173.7118419698019</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-34.994482795083705,173.7124948999284</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-34.9949796954883,173.71315250572724</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-34.99548186601158,173.7138134446796</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-34.995941245517926,173.71453353071846</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-34.996440754940856,173.71522230881422</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>-34.996949948255235,173.71589965488644</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>-34.997271393317206,173.71671901602704</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P547"/>
+  <dimension ref="A1:P552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29968,6 +29968,276 @@
         <v>332.03</v>
       </c>
       <c r="P547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>344.61</v>
+      </c>
+      <c r="C548" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D548" t="n">
+        <v>339.84</v>
+      </c>
+      <c r="E548" t="n">
+        <v>350.71</v>
+      </c>
+      <c r="F548" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="G548" t="n">
+        <v>338.05</v>
+      </c>
+      <c r="H548" t="n">
+        <v>344.1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>341.69</v>
+      </c>
+      <c r="J548" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="K548" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="L548" t="n">
+        <v>350.74</v>
+      </c>
+      <c r="M548" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="N548" t="n">
+        <v>324.5</v>
+      </c>
+      <c r="O548" t="n">
+        <v>332.57</v>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="C549" t="n">
+        <v>332.69</v>
+      </c>
+      <c r="D549" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="E549" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="F549" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="G549" t="n">
+        <v>338.68</v>
+      </c>
+      <c r="H549" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="I549" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="J549" t="n">
+        <v>343.11</v>
+      </c>
+      <c r="K549" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="L549" t="n">
+        <v>351.18</v>
+      </c>
+      <c r="M549" t="n">
+        <v>338.76</v>
+      </c>
+      <c r="N549" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="O549" t="n">
+        <v>333.27</v>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="C550" t="n">
+        <v>332.9</v>
+      </c>
+      <c r="D550" t="n">
+        <v>341.11</v>
+      </c>
+      <c r="E550" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="F550" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="G550" t="n">
+        <v>339.15</v>
+      </c>
+      <c r="H550" t="n">
+        <v>345.09</v>
+      </c>
+      <c r="I550" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="J550" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="K550" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="L550" t="n">
+        <v>351.53</v>
+      </c>
+      <c r="M550" t="n">
+        <v>338.98</v>
+      </c>
+      <c r="N550" t="n">
+        <v>325.72</v>
+      </c>
+      <c r="O550" t="n">
+        <v>333.67</v>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="C551" t="n">
+        <v>332.57</v>
+      </c>
+      <c r="D551" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="E551" t="n">
+        <v>351.59</v>
+      </c>
+      <c r="F551" t="n">
+        <v>339.78</v>
+      </c>
+      <c r="G551" t="n">
+        <v>339.24</v>
+      </c>
+      <c r="H551" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="I551" t="n">
+        <v>342.06</v>
+      </c>
+      <c r="J551" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="K551" t="n">
+        <v>345.97</v>
+      </c>
+      <c r="L551" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="M551" t="n">
+        <v>338.23</v>
+      </c>
+      <c r="N551" t="n">
+        <v>324.72</v>
+      </c>
+      <c r="O551" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>344.95</v>
+      </c>
+      <c r="C552" t="n">
+        <v>332.41</v>
+      </c>
+      <c r="D552" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="E552" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="F552" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="G552" t="n">
+        <v>339.62</v>
+      </c>
+      <c r="H552" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="I552" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="J552" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="K552" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="L552" t="n">
+        <v>351.06</v>
+      </c>
+      <c r="M552" t="n">
+        <v>338.12</v>
+      </c>
+      <c r="N552" t="n">
+        <v>324.82</v>
+      </c>
+      <c r="O552" t="n">
+        <v>333.56</v>
+      </c>
+      <c r="P552" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29984,7 +30254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B554"/>
+  <dimension ref="A1:B559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35527,6 +35797,56 @@
       </c>
       <c r="B554" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -35695,28 +36015,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04292552821238704</v>
+        <v>-0.0440018784805573</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004455330438971727</v>
+        <v>0.004768088830769068</v>
       </c>
       <c r="M2" t="n">
-        <v>4.102105928684986</v>
+        <v>4.070249351156577</v>
       </c>
       <c r="N2" t="n">
-        <v>25.39716114449232</v>
+        <v>25.17095416270917</v>
       </c>
       <c r="O2" t="n">
-        <v>5.039559618110725</v>
+        <v>5.017066290443965</v>
       </c>
       <c r="P2" t="n">
-        <v>346.7246506682147</v>
+        <v>346.7356146459065</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35773,28 +36093,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0615020504589136</v>
+        <v>-0.07241318183141575</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009961852078737343</v>
+        <v>0.01378322865423742</v>
       </c>
       <c r="M3" t="n">
-        <v>3.817662603952982</v>
+        <v>3.833739220314632</v>
       </c>
       <c r="N3" t="n">
-        <v>23.18804198262488</v>
+        <v>23.36866881044783</v>
       </c>
       <c r="O3" t="n">
-        <v>4.815396347407436</v>
+        <v>4.834115101075669</v>
       </c>
       <c r="P3" t="n">
-        <v>340.9290037330206</v>
+        <v>341.0401768495281</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35851,28 +36171,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007875499254918535</v>
+        <v>-0.003602445699164198</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000152339729354134</v>
+        <v>3.192691447151397e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.061389843119703</v>
+        <v>4.091928503190069</v>
       </c>
       <c r="N4" t="n">
-        <v>25.11018379761049</v>
+        <v>25.31636572729909</v>
       </c>
       <c r="O4" t="n">
-        <v>5.011006265971984</v>
+        <v>5.03153711377538</v>
       </c>
       <c r="P4" t="n">
-        <v>347.3291994688119</v>
+        <v>347.4461426965849</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35929,28 +36249,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1121951944996829</v>
+        <v>0.1044165253861014</v>
       </c>
       <c r="J5" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K5" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02912776496195235</v>
+        <v>0.02560076697701708</v>
       </c>
       <c r="M5" t="n">
-        <v>4.164035823208909</v>
+        <v>4.171440685894948</v>
       </c>
       <c r="N5" t="n">
-        <v>25.9243531453828</v>
+        <v>25.88923173662832</v>
       </c>
       <c r="O5" t="n">
-        <v>5.091596325847405</v>
+        <v>5.088146198433013</v>
       </c>
       <c r="P5" t="n">
-        <v>353.1280944810386</v>
+        <v>353.2072889956919</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36007,28 +36327,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1498021174964978</v>
+        <v>0.1386053477218886</v>
       </c>
       <c r="J6" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K6" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04161867933090724</v>
+        <v>0.03604309007597373</v>
       </c>
       <c r="M6" t="n">
-        <v>4.549860667936565</v>
+        <v>4.573426321392355</v>
       </c>
       <c r="N6" t="n">
-        <v>31.92937722040504</v>
+        <v>32.05474368036134</v>
       </c>
       <c r="O6" t="n">
-        <v>5.650608570800586</v>
+        <v>5.661690885271055</v>
       </c>
       <c r="P6" t="n">
-        <v>342.2689334369772</v>
+        <v>342.3829269147574</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36085,28 +36405,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1962946622348288</v>
+        <v>0.1833728377551387</v>
       </c>
       <c r="J7" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K7" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05733090743621372</v>
+        <v>0.05062147486817681</v>
       </c>
       <c r="M7" t="n">
-        <v>5.096640339397872</v>
+        <v>5.128662486845178</v>
       </c>
       <c r="N7" t="n">
-        <v>39.21261972650618</v>
+        <v>39.40880474392363</v>
       </c>
       <c r="O7" t="n">
-        <v>6.261998061841458</v>
+        <v>6.277643247582936</v>
       </c>
       <c r="P7" t="n">
-        <v>341.5393297272922</v>
+        <v>341.6707960870266</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36163,28 +36483,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1749975567224284</v>
+        <v>0.1640254970354621</v>
       </c>
       <c r="J8" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K8" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04607623462873567</v>
+        <v>0.04104404165224818</v>
       </c>
       <c r="M8" t="n">
-        <v>5.153537934916741</v>
+        <v>5.164314046507417</v>
       </c>
       <c r="N8" t="n">
-        <v>39.24091117435381</v>
+        <v>39.28166692906679</v>
       </c>
       <c r="O8" t="n">
-        <v>6.264256633819675</v>
+        <v>6.267508829596237</v>
       </c>
       <c r="P8" t="n">
-        <v>346.6970592230618</v>
+        <v>346.8086922403724</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36241,28 +36561,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.226694734036149</v>
+        <v>0.2150597218797031</v>
       </c>
       <c r="J9" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K9" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06707388795918534</v>
+        <v>0.06126795269237806</v>
       </c>
       <c r="M9" t="n">
-        <v>5.539695963301988</v>
+        <v>5.554607369832769</v>
       </c>
       <c r="N9" t="n">
-        <v>44.23999373489004</v>
+        <v>44.28382007317351</v>
       </c>
       <c r="O9" t="n">
-        <v>6.651315188358618</v>
+        <v>6.65460893465375</v>
       </c>
       <c r="P9" t="n">
-        <v>342.9794257567626</v>
+        <v>343.097806919994</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36319,28 +36639,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2916490518507736</v>
+        <v>0.2797692839897589</v>
       </c>
       <c r="J10" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K10" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1006145189011413</v>
+        <v>0.09408461919531252</v>
       </c>
       <c r="M10" t="n">
-        <v>5.800010841015016</v>
+        <v>5.814586800699696</v>
       </c>
       <c r="N10" t="n">
-        <v>47.05922606452339</v>
+        <v>47.0963994489441</v>
       </c>
       <c r="O10" t="n">
-        <v>6.85997274517351</v>
+        <v>6.862681651435108</v>
       </c>
       <c r="P10" t="n">
-        <v>342.3249623111168</v>
+        <v>342.4458363228861</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36397,28 +36717,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3275767938355374</v>
+        <v>0.3103968752242277</v>
       </c>
       <c r="J11" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K11" t="n">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1085620249559397</v>
+        <v>0.09864741220687379</v>
       </c>
       <c r="M11" t="n">
-        <v>6.183971085176525</v>
+        <v>6.224695574257844</v>
       </c>
       <c r="N11" t="n">
-        <v>54.53532136229497</v>
+        <v>55.01262087415785</v>
       </c>
       <c r="O11" t="n">
-        <v>7.384803407152757</v>
+        <v>7.417049337449351</v>
       </c>
       <c r="P11" t="n">
-        <v>347.5754551558657</v>
+        <v>347.7502533196246</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36475,28 +36795,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3716207878764427</v>
+        <v>0.3565934047886621</v>
       </c>
       <c r="J12" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K12" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1281135580689307</v>
+        <v>0.1197992861588866</v>
       </c>
       <c r="M12" t="n">
-        <v>6.293936727486058</v>
+        <v>6.314406900051513</v>
       </c>
       <c r="N12" t="n">
-        <v>57.97461563866174</v>
+        <v>58.19040617193689</v>
       </c>
       <c r="O12" t="n">
-        <v>7.614106358507329</v>
+        <v>7.628263640694184</v>
       </c>
       <c r="P12" t="n">
-        <v>350.2515708911938</v>
+        <v>350.4046822651248</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36553,28 +36873,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3620381836806866</v>
+        <v>0.3452508700294544</v>
       </c>
       <c r="J13" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K13" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08244302959850947</v>
+        <v>0.07613216067112383</v>
       </c>
       <c r="M13" t="n">
-        <v>7.770105447083965</v>
+        <v>7.780095945481132</v>
       </c>
       <c r="N13" t="n">
-        <v>89.98308902423658</v>
+        <v>90.09248087421638</v>
       </c>
       <c r="O13" t="n">
-        <v>9.485941651951933</v>
+        <v>9.491705899058207</v>
       </c>
       <c r="P13" t="n">
-        <v>339.0095452266918</v>
+        <v>339.180593941548</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36631,28 +36951,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2122059601800601</v>
+        <v>0.1978517105339769</v>
       </c>
       <c r="J14" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K14" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01792833150585493</v>
+        <v>0.01584310504635345</v>
       </c>
       <c r="M14" t="n">
-        <v>10.2095443549541</v>
+        <v>10.17956143952244</v>
       </c>
       <c r="N14" t="n">
-        <v>152.1568507356248</v>
+        <v>151.454068948895</v>
       </c>
       <c r="O14" t="n">
-        <v>12.33518750305908</v>
+        <v>12.30666766224289</v>
       </c>
       <c r="P14" t="n">
-        <v>328.0018320828246</v>
+        <v>328.1480865097582</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36709,28 +37029,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1689992136964681</v>
+        <v>0.1597019821482823</v>
       </c>
       <c r="J15" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K15" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03338585139544747</v>
+        <v>0.03030512859431922</v>
       </c>
       <c r="M15" t="n">
-        <v>5.932632069762017</v>
+        <v>5.9248640994557</v>
       </c>
       <c r="N15" t="n">
-        <v>51.00739061234274</v>
+        <v>50.82962077205391</v>
       </c>
       <c r="O15" t="n">
-        <v>7.141945856161522</v>
+        <v>7.129489516932746</v>
       </c>
       <c r="P15" t="n">
-        <v>334.3786908014668</v>
+        <v>334.4734144858887</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36768,7 +37088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P547"/>
+  <dimension ref="A1:P552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81577,6 +81897,416 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-34.989914457877546,173.70979951654834</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-34.99066674969449,173.70969551711383</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-34.99141219856182,173.70988865608444</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-34.99213098439686,173.71024274675918</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-34.992804890221365,173.71069076823372</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-34.993397257190736,173.71122847955917</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-34.99395416874922,173.7118463124137</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-34.99448041830832,173.71249758663512</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-34.99497741775435,173.71315516030046</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-34.995478299928514,173.713817473584</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-34.99593707463153,173.714537364917</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-34.99643552900571,173.71522641176097</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-34.996947267555996,173.71590167882763</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>-34.997267212540336,173.71672204922316</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-34.989914425908644,173.70980061153892</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-34.99066661113085,173.7096975921037</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-34.991411076314925,173.70989564635366</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-34.99212888853225,173.710247965761</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-34.99280102388639,173.71069696891837</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-34.993393782403615,173.7112339405994</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-34.99395110645153,173.71185033335027</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-34.99447909787753,173.7124990792499</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>-34.994974424161065,173.7131586491679</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>-34.99547572442399,173.71382038334806</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-34.99593391051073,173.71454027361906</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-34.996434241456434,173.7152274226318</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>-34.996942672071505,173.7159051484408</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>-34.99726179301465,173.7167259811436</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-34.98991427565464,173.70980575799462</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-34.990666457981476,173.70969988551357</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-34.99141000586365,173.7099023139949</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-34.992127069479764,173.71025249546048</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-34.9927975387391,173.7107025582674</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-34.993391190101946,173.71123801470847</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-34.99394810539966,173.71185427386783</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-34.994476655080526,173.7125018405871</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-34.994973447989324,173.713159786842</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-34.99547281872652,173.71382366615856</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-34.995931393596415,173.7145425873592</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-34.996432575216204,173.71522873081756</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>-34.99693792340409,173.71590873370732</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>-34.99725869614279,173.7167282279551</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-34.98991429803292,173.70980499150122</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-34.99066669864472,173.7096962815838</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-34.99141093819219,173.70989650669446</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-34.992127504470595,173.7102514122715</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-34.99279781101623,173.71070212159952</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-34.99339069370375,173.71123879485702</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-34.993949759040504,173.7118521025623</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-34.99447797551136,173.7125003479724</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-34.994976246348294,173.71315652550948</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-34.99547486592247,173.71382135326934</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-34.99593491727645,173.71453934812297</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-34.99643825558058,173.71522427109315</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>-34.99694558254503,173.71590295101916</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>-34.997261870436446,173.71672592497336</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-34.98991434918323,173.7098032395163</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-34.990666815329895,173.7096945342239</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-34.99141073100809,173.70989779720568</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-34.99212663448895,173.71025357864946</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-34.99279601398708,173.71070500360747</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-34.99338859780015,173.71124208881733</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-34.99394859536733,173.71185363051802</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-34.99447784346827,173.71250049723386</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-34.99497598603583,173.71315682888925</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-34.99547400742095,173.71382232319064</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-34.99593477345279,173.7145394803367</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-34.99643908870067,173.7152236170002</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>-34.99694481663094,173.71590352928803</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>-34.99725954778254,173.71672761008196</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P552"/>
+  <dimension ref="A1:P554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30238,6 +30238,114 @@
         <v>333.56</v>
       </c>
       <c r="P552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>344.83</v>
+      </c>
+      <c r="C553" t="n">
+        <v>331.74</v>
+      </c>
+      <c r="D553" t="n">
+        <v>340.48</v>
+      </c>
+      <c r="E553" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="F553" t="n">
+        <v>340.14</v>
+      </c>
+      <c r="G553" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="H553" t="n">
+        <v>344.62</v>
+      </c>
+      <c r="I553" t="n">
+        <v>341.58</v>
+      </c>
+      <c r="J553" t="n">
+        <v>342.37</v>
+      </c>
+      <c r="K553" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="L553" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="M553" t="n">
+        <v>336.94</v>
+      </c>
+      <c r="N553" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="O553" t="n">
+        <v>332.44</v>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="C554" t="n">
+        <v>332.18</v>
+      </c>
+      <c r="D554" t="n">
+        <v>340.71</v>
+      </c>
+      <c r="E554" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="F554" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="G554" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="H554" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="I554" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="J554" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="K554" t="n">
+        <v>345.34</v>
+      </c>
+      <c r="L554" t="n">
+        <v>349.85</v>
+      </c>
+      <c r="M554" t="n">
+        <v>336.01</v>
+      </c>
+      <c r="N554" t="n">
+        <v>322.88</v>
+      </c>
+      <c r="O554" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="P554" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30254,7 +30362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35847,6 +35955,26 @@
       </c>
       <c r="B559" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -36015,28 +36143,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0440018784805573</v>
+        <v>-0.04469537123844179</v>
       </c>
       <c r="J2" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004768088830769068</v>
+        <v>0.00495463621469272</v>
       </c>
       <c r="M2" t="n">
-        <v>4.070249351156577</v>
+        <v>4.05900262086055</v>
       </c>
       <c r="N2" t="n">
-        <v>25.17095416270917</v>
+        <v>25.08434241758234</v>
       </c>
       <c r="O2" t="n">
-        <v>5.017066290443965</v>
+        <v>5.008427140089226</v>
       </c>
       <c r="P2" t="n">
-        <v>346.7356146459065</v>
+        <v>346.7427201172766</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36093,28 +36221,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07241318183141575</v>
+        <v>-0.07707464075993516</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01378322865423742</v>
+        <v>0.015581766323434</v>
       </c>
       <c r="M3" t="n">
-        <v>3.833739220314632</v>
+        <v>3.842079652537281</v>
       </c>
       <c r="N3" t="n">
-        <v>23.36866881044783</v>
+        <v>23.46564496622247</v>
       </c>
       <c r="O3" t="n">
-        <v>4.834115101075669</v>
+        <v>4.844135110236137</v>
       </c>
       <c r="P3" t="n">
-        <v>341.0401768495281</v>
+        <v>341.0879125451153</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36171,28 +36299,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.003602445699164198</v>
+        <v>-0.008023852255255551</v>
       </c>
       <c r="J4" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>3.192691447151397e-05</v>
+        <v>0.0001585315548017219</v>
       </c>
       <c r="M4" t="n">
-        <v>4.091928503190069</v>
+        <v>4.103543255371767</v>
       </c>
       <c r="N4" t="n">
-        <v>25.31636572729909</v>
+        <v>25.38795897250539</v>
       </c>
       <c r="O4" t="n">
-        <v>5.03153711377538</v>
+        <v>5.038646541731756</v>
       </c>
       <c r="P4" t="n">
-        <v>347.4461426965849</v>
+        <v>347.4914210932457</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36249,28 +36377,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1044165253861014</v>
+        <v>0.1019717419618312</v>
       </c>
       <c r="J5" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02560076697701708</v>
+        <v>0.02457630778306064</v>
       </c>
       <c r="M5" t="n">
-        <v>4.171440685894948</v>
+        <v>4.170476954874541</v>
       </c>
       <c r="N5" t="n">
-        <v>25.88923173662832</v>
+        <v>25.84624852638933</v>
       </c>
       <c r="O5" t="n">
-        <v>5.088146198433013</v>
+        <v>5.083920586160776</v>
       </c>
       <c r="P5" t="n">
-        <v>353.2072889956919</v>
+        <v>353.2323043934343</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36327,28 +36455,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1386053477218886</v>
+        <v>0.1349784088844999</v>
       </c>
       <c r="J6" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K6" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03604309007597373</v>
+        <v>0.03437773559631074</v>
       </c>
       <c r="M6" t="n">
-        <v>4.573426321392355</v>
+        <v>4.577932169963585</v>
       </c>
       <c r="N6" t="n">
-        <v>32.05474368036134</v>
+        <v>32.04939156311521</v>
       </c>
       <c r="O6" t="n">
-        <v>5.661690885271055</v>
+        <v>5.661218204866795</v>
       </c>
       <c r="P6" t="n">
-        <v>342.3829269147574</v>
+        <v>342.420040789391</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36405,28 +36533,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1833728377551387</v>
+        <v>0.1788605174960766</v>
       </c>
       <c r="J7" t="n">
+        <v>553</v>
+      </c>
+      <c r="K7" t="n">
         <v>551</v>
       </c>
-      <c r="K7" t="n">
-        <v>549</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05062147486817681</v>
+        <v>0.04842266841679377</v>
       </c>
       <c r="M7" t="n">
-        <v>5.128662486845178</v>
+        <v>5.137663757929587</v>
       </c>
       <c r="N7" t="n">
-        <v>39.40880474392363</v>
+        <v>39.43688805400688</v>
       </c>
       <c r="O7" t="n">
-        <v>6.277643247582936</v>
+        <v>6.279879620980555</v>
       </c>
       <c r="P7" t="n">
-        <v>341.6707960870266</v>
+        <v>341.7169406567322</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36483,28 +36611,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1640254970354621</v>
+        <v>0.1598452037800061</v>
       </c>
       <c r="J8" t="n">
+        <v>553</v>
+      </c>
+      <c r="K8" t="n">
         <v>551</v>
       </c>
-      <c r="K8" t="n">
-        <v>549</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04104404165224818</v>
+        <v>0.03919906528745476</v>
       </c>
       <c r="M8" t="n">
-        <v>5.164314046507417</v>
+        <v>5.167697111320916</v>
       </c>
       <c r="N8" t="n">
-        <v>39.28166692906679</v>
+        <v>39.28576615141694</v>
       </c>
       <c r="O8" t="n">
-        <v>6.267508829596237</v>
+        <v>6.267835842730483</v>
       </c>
       <c r="P8" t="n">
-        <v>346.8086922403724</v>
+        <v>346.85144225253</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36561,28 +36689,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2150597218797031</v>
+        <v>0.2103164558999147</v>
       </c>
       <c r="J9" t="n">
+        <v>553</v>
+      </c>
+      <c r="K9" t="n">
         <v>551</v>
       </c>
-      <c r="K9" t="n">
-        <v>549</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.06126795269237806</v>
+        <v>0.05892901072850554</v>
       </c>
       <c r="M9" t="n">
-        <v>5.554607369832769</v>
+        <v>5.560832967986737</v>
       </c>
       <c r="N9" t="n">
-        <v>44.28382007317351</v>
+        <v>44.31166275476391</v>
       </c>
       <c r="O9" t="n">
-        <v>6.65460893465375</v>
+        <v>6.656700590740424</v>
       </c>
       <c r="P9" t="n">
-        <v>343.097806919994</v>
+        <v>343.1463160495905</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36639,28 +36767,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2797692839897589</v>
+        <v>0.2747656151016977</v>
       </c>
       <c r="J10" t="n">
+        <v>553</v>
+      </c>
+      <c r="K10" t="n">
         <v>551</v>
       </c>
-      <c r="K10" t="n">
-        <v>549</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.09408461919531252</v>
+        <v>0.09130132292411919</v>
       </c>
       <c r="M10" t="n">
-        <v>5.814586800699696</v>
+        <v>5.821569030262038</v>
       </c>
       <c r="N10" t="n">
-        <v>47.0963994489441</v>
+        <v>47.13525856534019</v>
       </c>
       <c r="O10" t="n">
-        <v>6.862681651435108</v>
+        <v>6.865512258043109</v>
       </c>
       <c r="P10" t="n">
-        <v>342.4458363228861</v>
+        <v>342.497009595038</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36717,28 +36845,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3103968752242277</v>
+        <v>0.3034449158277077</v>
       </c>
       <c r="J11" t="n">
+        <v>553</v>
+      </c>
+      <c r="K11" t="n">
         <v>551</v>
       </c>
-      <c r="K11" t="n">
-        <v>549</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09864741220687379</v>
+        <v>0.09469989541518364</v>
       </c>
       <c r="M11" t="n">
-        <v>6.224695574257844</v>
+        <v>6.241360026131678</v>
       </c>
       <c r="N11" t="n">
-        <v>55.01262087415785</v>
+        <v>55.21805489680499</v>
       </c>
       <c r="O11" t="n">
-        <v>7.417049337449351</v>
+        <v>7.430885202773959</v>
       </c>
       <c r="P11" t="n">
-        <v>347.7502533196246</v>
+        <v>347.8213540879831</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36795,28 +36923,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3565934047886621</v>
+        <v>0.3499834275906357</v>
       </c>
       <c r="J12" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K12" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1197992861588866</v>
+        <v>0.1160321032818208</v>
       </c>
       <c r="M12" t="n">
-        <v>6.314406900051513</v>
+        <v>6.325400563691054</v>
       </c>
       <c r="N12" t="n">
-        <v>58.19040617193689</v>
+        <v>58.34448402955638</v>
       </c>
       <c r="O12" t="n">
-        <v>7.628263640694184</v>
+        <v>7.638356107799399</v>
       </c>
       <c r="P12" t="n">
-        <v>350.4046822651248</v>
+        <v>350.4723762520994</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36873,28 +37001,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3452508700294544</v>
+        <v>0.3373536484704814</v>
       </c>
       <c r="J13" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K13" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07613216067112383</v>
+        <v>0.07305391466975286</v>
       </c>
       <c r="M13" t="n">
-        <v>7.780095945481132</v>
+        <v>7.789764666947073</v>
       </c>
       <c r="N13" t="n">
-        <v>90.09248087421638</v>
+        <v>90.28764377355482</v>
       </c>
       <c r="O13" t="n">
-        <v>9.491705899058207</v>
+        <v>9.501981044685094</v>
       </c>
       <c r="P13" t="n">
-        <v>339.180593941548</v>
+        <v>339.2614741105701</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36951,28 +37079,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1978517105339769</v>
+        <v>0.1911078373385602</v>
       </c>
       <c r="J14" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K14" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01584310504635345</v>
+        <v>0.0148695664732289</v>
       </c>
       <c r="M14" t="n">
-        <v>10.17956143952244</v>
+        <v>10.17173688946569</v>
       </c>
       <c r="N14" t="n">
-        <v>151.454068948895</v>
+        <v>151.2860695151909</v>
       </c>
       <c r="O14" t="n">
-        <v>12.30666766224289</v>
+        <v>12.299840223157</v>
       </c>
       <c r="P14" t="n">
-        <v>328.1480865097582</v>
+        <v>328.217153838148</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37029,28 +37157,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1597019821482823</v>
+        <v>0.1549882025982796</v>
       </c>
       <c r="J15" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K15" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03030512859431922</v>
+        <v>0.02869772515367686</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9248640994557</v>
+        <v>5.926902092180388</v>
       </c>
       <c r="N15" t="n">
-        <v>50.82962077205391</v>
+        <v>50.83358422930195</v>
       </c>
       <c r="O15" t="n">
-        <v>7.129489516932746</v>
+        <v>7.129767473719038</v>
       </c>
       <c r="P15" t="n">
-        <v>334.4734144858887</v>
+        <v>334.5216967078401</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37088,7 +37216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P552"/>
+  <dimension ref="A1:P554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82307,6 +82435,170 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-34.98991438754594,173.70980192552761</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-34.99066730394877,173.70968721715428</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-34.99141109358025,173.70989553881105</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-34.99212659494431,173.7102536771212</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-34.99279585062078,173.71070526560817</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-34.99338992152875,173.71124000842136</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-34.99395098395962,173.71185049418773</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-34.994481144545254,173.71249676569695</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-34.994979239941514,173.71315303664187</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-34.99547645084835,173.7138195626454</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-34.99594182081259,173.71453300186343</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-34.99644802580693,173.7152166003657</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>-34.99695462033097,173.71589612744575</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>-34.99726821902367,173.7167213190093</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-34.989914608131286,173.7097943700926</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-34.99066698306479,173.70969202239405</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-34.991410696477416,173.7098980122909</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-34.992122838204885,173.71026303193455</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-34.99279089517639,173.71071321296273</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-34.99338595034286,173.71124624960905</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-34.993947982907756,173.7118544347053</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-34.99447989013601,173.71249818368105</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-34.99497917486342,173.71315311248685</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-34.995479026352854,173.71381665288126</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-34.99594347478474,173.71453148140526</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>-34.99645506945818,173.71521107030526</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>-34.99695967536363,173.71589231087017</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>-34.99728114846294,173.7167119385682</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
